--- a/results/03_LDA_Classification/tables/lda_env_significance.xlsx
+++ b/results/03_LDA_Classification/tables/lda_env_significance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,11 +449,6 @@
           <t>Cluster C2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster C3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -471,17 +466,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.35 ± 0.12</t>
+          <t>1.39 ± 0.10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>-1.17 ± 0.08</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1.60 ± 0.14</t>
         </is>
       </c>
     </row>
@@ -491,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Measured Depth (m)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -501,17 +491,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.74 ± 0.34</t>
+          <t>1.26 ± 0.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.10 ± 0.84</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>4.79 ± 0.94</t>
+          <t>1.55 ± 0.18</t>
         </is>
       </c>
     </row>
@@ -521,7 +506,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Measured Depth (m)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,17 +516,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.22 ± 0.08</t>
+          <t>3.08 ± 0.34</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.55 ± 0.18</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1.45 ± 0.28</t>
+          <t>4.10 ± 0.84</t>
         </is>
       </c>
     </row>
@@ -561,17 +541,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.64 ± 0.44</t>
+          <t>19.91 ± 0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>19.94 ± 0.26</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>21.25 ± 0.31</t>
         </is>
       </c>
     </row>
@@ -591,17 +566,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.64 ± 0.11</t>
+          <t>9.56 ± 0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>9.53 ± 0.25</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>9.13 ± 0.44</t>
         </is>
       </c>
     </row>
@@ -613,7 +583,6 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -626,13 +595,10 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -643,7 +609,6 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -657,7 +622,6 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/03_LDA_Classification/tables/lda_env_significance.xlsx
+++ b/results/03_LDA_Classification/tables/lda_env_significance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>Cluster C2</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster C3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -456,7 +461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MPS (Phi)</t>
+          <t>Measured Depth (m)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,12 +471,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.39 ± 0.10</t>
+          <t>3.64 ± 0.61</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.17 ± 0.08</t>
+          <t>9.35 ± 0.98</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3.12 ± 0.57</t>
         </is>
       </c>
     </row>
@@ -481,7 +491,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -491,12 +501,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.26 ± 0.08</t>
+          <t>9.60 ± 0.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.55 ± 0.18</t>
+          <t>8.94 ± 0.61</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9.32 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -506,7 +521,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Measured Depth (m)</t>
+          <t>MPS (Phi)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -516,12 +531,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.08 ± 0.34</t>
+          <t>1.28 ± 0.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4.10 ± 0.84</t>
+          <t>0.67 ± 0.25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1.38 ± 0.12</t>
         </is>
       </c>
     </row>
@@ -541,12 +561,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.91 ± 0.38</t>
+          <t>20.78 ± 0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.94 ± 0.26</t>
+          <t>18.13 ± 0.72</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>19.60 ± 0.51</t>
         </is>
       </c>
     </row>
@@ -556,7 +581,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -566,12 +591,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.56 ± 0.12</t>
+          <t>1.83 ± 0.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9.53 ± 0.25</t>
+          <t>2.06 ± 0.42</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2.06 ± 0.34</t>
         </is>
       </c>
     </row>
@@ -583,6 +613,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -595,10 +626,13 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -609,6 +643,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -622,6 +657,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
